--- a/02_HRvLR_groups/Figures/S01_Volcano/c_data/s01_volcano.xlsx
+++ b/02_HRvLR_groups/Figures/S01_Volcano/c_data/s01_volcano.xlsx
@@ -359,10 +359,10 @@
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Pathways/03_Contrasts/c_data/set_tests.rds</t>
-  </si>
-  <si>
-    <t>52c365ae84d1f5f25d3e280360d861dd</t>
+    <t>02_HRvLR_groups/03_Pathways/c_data/set_tests.rds</t>
+  </si>
+  <si>
+    <t>068c220be1f09313a9955fa01f855602</t>
   </si>
   <si>
     <t>package</t>

--- a/02_HRvLR_groups/Figures/S01_Volcano/c_data/s01_volcano.xlsx
+++ b/02_HRvLR_groups/Figures/S01_Volcano/c_data/s01_volcano.xlsx
@@ -426,7 +426,7 @@
     <t>02_HRvLR_groups/03_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>068c220be1f09313a9955fa01f855602</t>
+    <t>b928dfb75f0631b92e8ffaf819778f86</t>
   </si>
   <si>
     <t>BiocGenerics</t>
